--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484818_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484818_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.877</v>
+        <v>7.8332</v>
       </c>
       <c r="E2" t="n">
-        <v>5.9177</v>
+        <v>5.4507</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9592</v>
+        <v>2.3825</v>
       </c>
       <c r="G2" t="n">
         <v>5.4677</v>
@@ -610,13 +610,13 @@
         <v>1.3209</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9564</v>
+        <v>0.9127</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5495</v>
+        <v>1.0825</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5931</v>
+        <v>-0.1698</v>
       </c>
       <c r="V2" t="n">
         <v>1.2642</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.9215</v>
+        <v>5.5279</v>
       </c>
       <c r="E3" t="n">
-        <v>4.2639</v>
+        <v>3.7381</v>
       </c>
       <c r="F3" t="n">
-        <v>1.6575</v>
+        <v>1.7898</v>
       </c>
       <c r="G3" t="n">
         <v>6.6049</v>
@@ -688,13 +688,13 @@
         <v>0.9435</v>
       </c>
       <c r="S3" t="n">
-        <v>1.0905</v>
+        <v>0.6969</v>
       </c>
       <c r="T3" t="n">
-        <v>1.6794</v>
+        <v>1.1536</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.589</v>
+        <v>-0.4567</v>
       </c>
       <c r="V3" t="n">
         <v>0.3018</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.6424</v>
+        <v>4.8554</v>
       </c>
       <c r="E4" t="n">
-        <v>3.7042</v>
+        <v>3.9965</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9382</v>
+        <v>0.8588</v>
       </c>
       <c r="G4" t="n">
         <v>2.2638</v>
@@ -766,13 +766,13 @@
         <v>0.7548</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8476</v>
+        <v>-0.6347</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2105</v>
+        <v>0.0818</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6371</v>
+        <v>-0.7165</v>
       </c>
       <c r="V4" t="n">
         <v>2.4714</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.5544</v>
+        <v>4.837</v>
       </c>
       <c r="E5" t="n">
-        <v>3.3558</v>
+        <v>3.4533</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1986</v>
+        <v>1.3837</v>
       </c>
       <c r="G5" t="n">
         <v>2.699</v>
@@ -844,13 +844,13 @@
         <v>0.5661</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5972</v>
+        <v>-0.3146</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3281</v>
+        <v>-0.2306</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2692</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="V5" t="n">
         <v>3.7736</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4.4744</v>
+        <v>3.6119</v>
       </c>
       <c r="E6" t="n">
-        <v>2.4452</v>
+        <v>2.2705</v>
       </c>
       <c r="F6" t="n">
-        <v>2.0292</v>
+        <v>1.3414</v>
       </c>
       <c r="G6" t="n">
         <v>0.2892</v>
@@ -922,13 +922,13 @@
         <v>0.9435</v>
       </c>
       <c r="S6" t="n">
-        <v>1.8835</v>
+        <v>1.021</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7359</v>
+        <v>0.5612</v>
       </c>
       <c r="U6" t="n">
-        <v>1.1476</v>
+        <v>0.4598</v>
       </c>
       <c r="V6" t="n">
         <v>2.4904</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>H. SERRANO BOIX</t>
+          <t>M. RODILLA ALCAIDE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.9906</v>
+        <v>2.452</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2094</v>
+        <v>2.7189</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7812</v>
+        <v>-0.2669</v>
       </c>
       <c r="G7" t="n">
-        <v>2.1629</v>
+        <v>1.3405</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.331</v>
+        <v>-0.4281</v>
       </c>
       <c r="I7" t="n">
-        <v>2.4939</v>
+        <v>1.7686</v>
       </c>
       <c r="J7" t="n">
-        <v>1.7262</v>
+        <v>1.2509</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4015</v>
+        <v>0.3702</v>
       </c>
       <c r="L7" t="n">
-        <v>1.3247</v>
+        <v>0.8808</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4367</v>
+        <v>0.0896</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7325</v>
+        <v>-0.7982</v>
       </c>
       <c r="O7" t="n">
-        <v>1.1692</v>
+        <v>0.8878</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.1887</v>
+        <v>-1.1322</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9435</v>
+        <v>-1.887</v>
       </c>
       <c r="R7" t="n">
         <v>0.7548</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0165</v>
+        <v>-0.5675</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4267</v>
+        <v>-0.3807</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4103</v>
+        <v>-0.1869</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>2.8112</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>3.7356</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.9244</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. RODILLA ALCAIDE</t>
+          <t>H. SERRANO BOIX</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.7221</v>
+        <v>2.1591</v>
       </c>
       <c r="E8" t="n">
-        <v>2.4652</v>
+        <v>1.4043</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7431</v>
+        <v>0.7548</v>
       </c>
       <c r="G8" t="n">
-        <v>1.3405</v>
+        <v>2.1629</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4281</v>
+        <v>-0.331</v>
       </c>
       <c r="I8" t="n">
-        <v>1.7686</v>
+        <v>2.4939</v>
       </c>
       <c r="J8" t="n">
-        <v>1.2509</v>
+        <v>1.7262</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3702</v>
+        <v>0.4015</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8808</v>
+        <v>1.3247</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0896</v>
+        <v>0.4367</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7982</v>
+        <v>-0.7325</v>
       </c>
       <c r="O8" t="n">
-        <v>0.8878</v>
+        <v>1.1692</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.1322</v>
+        <v>-0.1887</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.887</v>
+        <v>-0.9435</v>
       </c>
       <c r="R8" t="n">
         <v>0.7548</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.2974</v>
+        <v>0.1849</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6343</v>
+        <v>0.6216</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6631</v>
+        <v>-0.4367</v>
       </c>
       <c r="V8" t="n">
-        <v>2.8112</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>3.7356</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.9244</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. MALLIK BOUNAD</t>
+          <t>J. DALMAU ROIG</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4125</v>
+        <v>0.8066</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.5248</v>
+        <v>-0.7052</v>
       </c>
       <c r="F9" t="n">
-        <v>2.9373</v>
+        <v>1.5119</v>
       </c>
       <c r="G9" t="n">
-        <v>1.8565</v>
+        <v>0.7336</v>
       </c>
       <c r="H9" t="n">
-        <v>2.6209</v>
+        <v>0.097</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7644</v>
+        <v>0.6365</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6506</v>
+        <v>-0.515</v>
       </c>
       <c r="K9" t="n">
-        <v>1.8915</v>
+        <v>-0.6965</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.241</v>
+        <v>0.1816</v>
       </c>
       <c r="M9" t="n">
-        <v>1.2059</v>
+        <v>1.2485</v>
       </c>
       <c r="N9" t="n">
-        <v>0.7294</v>
+        <v>0.7936</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4765</v>
+        <v>0.455</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.5096</v>
+        <v>0.9435</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.0192</v>
+        <v>-0.1887</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5096</v>
+        <v>1.1322</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3675</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.458</v>
+        <v>-0.3034</v>
       </c>
       <c r="U9" t="n">
-        <v>0.8254</v>
+        <v>0.3763</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3018</v>
+        <v>-0.9434</v>
       </c>
       <c r="W9" t="n">
         <v>0.3018</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.6036</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. DALMAU ROIG</t>
+          <t>R. MALLIK BOUNAD</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3522</v>
+        <v>0.7792</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2126</v>
+        <v>-1.92</v>
       </c>
       <c r="F10" t="n">
-        <v>1.5648</v>
+        <v>2.6992</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7336</v>
+        <v>1.8565</v>
       </c>
       <c r="H10" t="n">
-        <v>0.097</v>
+        <v>2.6209</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6365</v>
+        <v>-0.7644</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.515</v>
+        <v>0.6506</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6965</v>
+        <v>1.8915</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1816</v>
+        <v>-1.241</v>
       </c>
       <c r="M10" t="n">
-        <v>1.2485</v>
+        <v>1.2059</v>
       </c>
       <c r="N10" t="n">
-        <v>0.7936</v>
+        <v>0.7294</v>
       </c>
       <c r="O10" t="n">
-        <v>0.455</v>
+        <v>0.4765</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9435</v>
+        <v>-1.5096</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.1887</v>
+        <v>-3.0192</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1322</v>
+        <v>1.5096</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3815</v>
+        <v>0.7341</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8107</v>
+        <v>0.1468</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4292</v>
+        <v>0.5873</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.9434</v>
+        <v>-0.3018</v>
       </c>
       <c r="W10" t="n">
         <v>0.3018</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2452</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.7594</v>
+        <v>-1.1575</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4364</v>
+        <v>0.1441</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1958</v>
+        <v>-1.3016</v>
       </c>
       <c r="G11" t="n">
         <v>1.4553</v>
@@ -1312,13 +1312,13 @@
         <v>0.5661</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0688</v>
+        <v>-0.3293</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2039</v>
+        <v>-0.08840000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1351</v>
+        <v>-0.2409</v>
       </c>
       <c r="V11" t="n">
         <v>0.9244</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.1204</v>
+        <v>-2.0494</v>
       </c>
       <c r="E12" t="n">
-        <v>0.06</v>
+        <v>0.1575</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.1804</v>
+        <v>-2.2068</v>
       </c>
       <c r="G12" t="n">
         <v>1.2926</v>
@@ -1390,13 +1390,13 @@
         <v>0.1887</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1341</v>
+        <v>0.205</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4732</v>
+        <v>0.5706</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3391</v>
+        <v>-0.3656</v>
       </c>
       <c r="V12" t="n">
         <v>-2.7922</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>29.0673</v>
+        <v>29.65540000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>20.1204</v>
+        <v>20.7087</v>
       </c>
       <c r="F13" t="n">
-        <v>8.946699999999998</v>
+        <v>8.9468</v>
       </c>
       <c r="G13" t="n">
         <v>26.166</v>
@@ -1447,7 +1447,7 @@
         <v>11.3867</v>
       </c>
       <c r="L13" t="n">
-        <v>8.223400000000002</v>
+        <v>8.2234</v>
       </c>
       <c r="M13" t="n">
         <v>6.555899999999999</v>
@@ -1456,7 +1456,7 @@
         <v>-2.2144</v>
       </c>
       <c r="O13" t="n">
-        <v>8.770300000000001</v>
+        <v>8.770299999999999</v>
       </c>
       <c r="P13" t="n">
         <v>-8.491499999999998</v>
@@ -1465,16 +1465,16 @@
         <v>-17.9265</v>
       </c>
       <c r="R13" t="n">
-        <v>9.435</v>
+        <v>9.435000000000002</v>
       </c>
       <c r="S13" t="n">
-        <v>1.3936</v>
+        <v>1.9814</v>
       </c>
       <c r="T13" t="n">
-        <v>2.627000000000001</v>
+        <v>3.215</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.2338</v>
+        <v>-1.2337</v>
       </c>
       <c r="V13" t="n">
         <v>9.999600000000001</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.8872</v>
+        <v>1.0307</v>
       </c>
       <c r="E15" t="n">
-        <v>4.3292</v>
+        <v>3.16</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.442</v>
+        <v>-2.1293</v>
       </c>
       <c r="G15" t="n">
         <v>-1.5694</v>
@@ -1624,13 +1624,13 @@
         <v>1.887</v>
       </c>
       <c r="S15" t="n">
-        <v>1.5507</v>
+        <v>0.6942</v>
       </c>
       <c r="T15" t="n">
-        <v>2.202</v>
+        <v>1.0328</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6513</v>
+        <v>-0.3386</v>
       </c>
       <c r="V15" t="n">
         <v>0.9624</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2795</v>
+        <v>0.5501</v>
       </c>
       <c r="E16" t="n">
-        <v>1.192</v>
+        <v>0.3151</v>
       </c>
       <c r="F16" t="n">
-        <v>0.08749999999999999</v>
+        <v>0.2351</v>
       </c>
       <c r="G16" t="n">
         <v>-1.0289</v>
@@ -1702,13 +1702,13 @@
         <v>1.3209</v>
       </c>
       <c r="S16" t="n">
-        <v>0.9875</v>
+        <v>0.2582</v>
       </c>
       <c r="T16" t="n">
-        <v>1.0669</v>
+        <v>0.19</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0793</v>
+        <v>0.0682</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. DOMINGUEZ CARRAL</t>
+          <t>F. ALEMANY GARCIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6706</v>
+        <v>-0.8172</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3381</v>
+        <v>2.5784</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3325</v>
+        <v>-3.3956</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.709</v>
+        <v>0.7856</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2152</v>
+        <v>1.8289</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.4937</v>
+        <v>-1.0433</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.522</v>
+        <v>2.4966</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7771</v>
+        <v>2.4143</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.2991</v>
+        <v>0.0823</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.1869</v>
+        <v>-1.7109</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.9923</v>
+        <v>-0.5854</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1946</v>
+        <v>-1.1256</v>
       </c>
       <c r="P19" t="n">
         <v>0.7548</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6983</v>
+        <v>0.7548</v>
       </c>
       <c r="S19" t="n">
-        <v>0.9441000000000001</v>
+        <v>0.4346</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2409</v>
+        <v>0.0818</v>
       </c>
       <c r="U19" t="n">
-        <v>0.7030999999999999</v>
+        <v>0.3527</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.6606</v>
+        <v>-2.7922</v>
       </c>
       <c r="W19" t="n">
-        <v>0.8865</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.547</v>
+        <v>-2.7922</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>F. ALEMANY GARCIA</t>
+          <t>A. DOMINGUEZ CARRAL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9314</v>
+        <v>-1.0085</v>
       </c>
       <c r="E20" t="n">
-        <v>2.6758</v>
+        <v>-0.4356</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.6073</v>
+        <v>-0.573</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7856</v>
+        <v>-1.709</v>
       </c>
       <c r="H20" t="n">
-        <v>1.8289</v>
+        <v>-0.2152</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.0433</v>
+        <v>-1.4937</v>
       </c>
       <c r="J20" t="n">
-        <v>2.4966</v>
+        <v>-0.522</v>
       </c>
       <c r="K20" t="n">
-        <v>2.4143</v>
+        <v>0.7771</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0823</v>
+        <v>-1.2991</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.7109</v>
+        <v>-1.1869</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5854</v>
+        <v>-0.9923</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.1256</v>
+        <v>-0.1946</v>
       </c>
       <c r="P20" t="n">
         <v>0.7548</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7548</v>
+        <v>1.6983</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3204</v>
+        <v>0.6062</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1793</v>
+        <v>0.1435</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1411</v>
+        <v>0.4627</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.7922</v>
+        <v>-0.6606</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.8865</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.7922</v>
+        <v>-1.547</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5559</v>
+        <v>-1.3477</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0495</v>
+        <v>0.3418</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.6054</v>
+        <v>-1.6895</v>
       </c>
       <c r="G21" t="n">
         <v>0.08599999999999999</v>
@@ -2092,13 +2092,13 @@
         <v>1.887</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2069</v>
+        <v>0.4151</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2076</v>
+        <v>0.0847</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4145</v>
+        <v>0.3304</v>
       </c>
       <c r="V21" t="n">
         <v>-1.8488</v>
@@ -2125,10 +2125,10 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.3158</v>
+        <v>-1.8286</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.7147</v>
+        <v>-1.2275</v>
       </c>
       <c r="F22" t="n">
         <v>-0.6011</v>
@@ -2170,10 +2170,10 @@
         <v>1.3209</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9188</v>
+        <v>-0.4317</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1735</v>
+        <v>0.3137</v>
       </c>
       <c r="U22" t="n">
         <v>-0.7454</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>V. CARLES TEJEDO</t>
+          <t>J. ARTIGUES DANOBEITIA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.8324</v>
+        <v>-2.9595</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.1945</v>
+        <v>-1.3865</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.6378</v>
+        <v>-1.5731</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.5806</v>
+        <v>-1.8273</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.4962</v>
+        <v>-1.4094</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.0844</v>
+        <v>-0.4178</v>
       </c>
       <c r="J23" t="n">
-        <v>0.5545</v>
+        <v>0.8749</v>
       </c>
       <c r="K23" t="n">
-        <v>1.1629</v>
+        <v>-0.4171</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6084000000000001</v>
+        <v>1.2921</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.1351</v>
+        <v>-2.7022</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.6591</v>
+        <v>-0.9923</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.476</v>
+        <v>-1.7099</v>
       </c>
       <c r="P23" t="n">
-        <v>0.7548</v>
+        <v>0.3774</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9435</v>
+        <v>-1.887</v>
       </c>
       <c r="R23" t="n">
-        <v>1.6983</v>
+        <v>2.2644</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5162</v>
+        <v>-0.5663</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1945</v>
+        <v>-0.6762</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.7107</v>
+        <v>0.11</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.4904</v>
+        <v>-0.9434</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.3018</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.4904</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. ARTIGUES DANOBEITIA</t>
+          <t>V. CARLES TEJEDO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.101</v>
+        <v>-3.5437</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.8737</v>
+        <v>-0.1945</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.2273</v>
+        <v>-3.3492</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.8273</v>
+        <v>-1.5806</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.4094</v>
+        <v>-0.4962</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.4178</v>
+        <v>-1.0844</v>
       </c>
       <c r="J24" t="n">
-        <v>0.8749</v>
+        <v>0.5545</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.4171</v>
+        <v>1.1629</v>
       </c>
       <c r="L24" t="n">
-        <v>1.2921</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.7022</v>
+        <v>-2.1351</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.9923</v>
+        <v>-1.6591</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.7099</v>
+        <v>-0.476</v>
       </c>
       <c r="P24" t="n">
-        <v>0.3774</v>
+        <v>0.7548</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.887</v>
+        <v>-0.9435</v>
       </c>
       <c r="R24" t="n">
-        <v>2.2644</v>
+        <v>1.6983</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.7077</v>
+        <v>-0.2275</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.1634</v>
+        <v>0.1945</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5443</v>
+        <v>-0.422</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.9434</v>
+        <v>-2.4904</v>
       </c>
       <c r="W24" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.2452</v>
+        <v>-2.4904</v>
       </c>
     </row>
     <row r="25">
@@ -2359,10 +2359,10 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.4161</v>
+        <v>-5.2212</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.8941</v>
+        <v>-3.6992</v>
       </c>
       <c r="F25" t="n">
         <v>-1.522</v>
@@ -2404,10 +2404,10 @@
         <v>0.3774</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.8847</v>
+        <v>-0.6898</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.458</v>
+        <v>-0.2631</v>
       </c>
       <c r="U25" t="n">
         <v>-0.4267</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-6.8039</v>
+        <v>-5.4759</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.8145</v>
+        <v>-4.0351</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.9893</v>
+        <v>-1.4409</v>
       </c>
       <c r="G26" t="n">
         <v>-7.0553</v>
@@ -2482,13 +2482,13 @@
         <v>2.2644</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.673</v>
+        <v>-0.3451</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.5014999999999999</v>
+        <v>0.278</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.1715</v>
+        <v>-0.6231</v>
       </c>
       <c r="V26" t="n">
         <v>0.6036</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-9.759600000000001</v>
+        <v>-9.605600000000001</v>
       </c>
       <c r="E27" t="n">
         <v>-7.5163</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.2433</v>
+        <v>-2.0893</v>
       </c>
       <c r="G27" t="n">
         <v>-8.4346</v>
@@ -2560,13 +2560,13 @@
         <v>2.4531</v>
       </c>
       <c r="S27" t="n">
-        <v>0.2974</v>
+        <v>0.4514</v>
       </c>
       <c r="T27" t="n">
         <v>-0.1459</v>
       </c>
       <c r="U27" t="n">
-        <v>0.4433</v>
+        <v>0.5973000000000001</v>
       </c>
       <c r="V27" t="n">
         <v>-3.132</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-29.0673</v>
+        <v>-27.0744</v>
       </c>
       <c r="E28" t="n">
-        <v>-8.9467</v>
+        <v>-8.946699999999998</v>
       </c>
       <c r="F28" t="n">
-        <v>-20.1205</v>
+        <v>-18.1279</v>
       </c>
       <c r="G28" t="n">
         <v>-26.1658</v>
@@ -2638,16 +2638,16 @@
         <v>17.9265</v>
       </c>
       <c r="S28" t="n">
-        <v>-1.3934</v>
+        <v>0.5993000000000002</v>
       </c>
       <c r="T28" t="n">
-        <v>1.2337</v>
+        <v>1.2338</v>
       </c>
       <c r="U28" t="n">
-        <v>-2.6272</v>
+        <v>-0.6345</v>
       </c>
       <c r="V28" t="n">
-        <v>-9.999599999999999</v>
+        <v>-9.999600000000001</v>
       </c>
       <c r="W28" t="n">
         <v>5.8103</v>
